--- a/Cairo_Giza_Final_Verified_POIs.xlsx
+++ b/Cairo_Giza_Final_Verified_POIs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abraam Refaat\Documents\GitHub\Nile-Quest---Graduation-Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59E33C59-6EED-465E-A60C-033F5B17F8A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20D1CE37-4E72-4A7B-A981-6B84862FDE33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1205" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="415">
   <si>
     <t>Name</t>
   </si>
@@ -1256,13 +1256,22 @@
   </si>
   <si>
     <t>Indoor/Outdoor</t>
+  </si>
+  <si>
+    <t>Saladin Citadel</t>
+  </si>
+  <si>
+    <t>30.0287° N, 31.2597° E</t>
+  </si>
+  <si>
+    <t>Citadel</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1277,6 +1286,18 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1314,11 +1335,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1623,7 +1646,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H172"/>
+  <dimension ref="A1:H173"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
@@ -6023,7 +6046,34 @@
         <v>411</v>
       </c>
     </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A173" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="B173" t="s">
+        <v>413</v>
+      </c>
+      <c r="C173" t="s">
+        <v>323</v>
+      </c>
+      <c r="D173" t="s">
+        <v>414</v>
+      </c>
+      <c r="E173" t="s">
+        <v>379</v>
+      </c>
+      <c r="F173" s="3">
+        <v>500</v>
+      </c>
+      <c r="G173" t="s">
+        <v>380</v>
+      </c>
+      <c r="H173" t="s">
+        <v>411</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>